--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487659_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487659_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6742</v>
+        <v>8.2174</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1449</v>
+        <v>5.9061</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5294</v>
+        <v>2.3113</v>
       </c>
       <c r="G2" t="n">
         <v>6.5858</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8356</v>
+        <v>-0.0743</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2282</v>
+        <v>0.0101</v>
       </c>
       <c r="V2" t="n">
         <v>0.7257</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9629</v>
+        <v>3.3353</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0694</v>
+        <v>4.8669</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1065</v>
+        <v>-1.5316</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5876</v>
+        <v>4.0257</v>
       </c>
       <c r="H3" t="n">
-        <v>2.769</v>
+        <v>1.6255</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8186</v>
+        <v>2.4002</v>
       </c>
       <c r="J3" t="n">
-        <v>3.462</v>
+        <v>6.0806</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2996</v>
+        <v>2.4346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1624</v>
+        <v>3.646</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1256</v>
+        <v>-2.0548</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5306</v>
+        <v>-0.8091</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6562</v>
+        <v>-1.2458</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-4.8508</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7463</v>
+        <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2429</v>
+        <v>-0.74</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0134</v>
+        <v>-0.3166</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2564</v>
+        <v>-0.4234</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1579</v>
+        <v>2.1839</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5642</v>
+        <v>3.9537</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7221</v>
+        <v>-1.7698</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3227</v>
+        <v>3.0384</v>
       </c>
       <c r="E4" t="n">
-        <v>4.045</v>
+        <v>3.0905</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7223</v>
+        <v>-0.052</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0257</v>
+        <v>3.5876</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6255</v>
+        <v>2.769</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4002</v>
+        <v>0.8186</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0806</v>
+        <v>3.462</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4346</v>
+        <v>3.2996</v>
       </c>
       <c r="L4" t="n">
-        <v>3.646</v>
+        <v>0.1624</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0548</v>
+        <v>0.1256</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8091</v>
+        <v>-0.5306</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2458</v>
+        <v>0.6562</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1344</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8508</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7526</v>
+        <v>-0.1674</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1384</v>
+        <v>0.0345</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6141</v>
+        <v>-0.2019</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1839</v>
+        <v>-1.1579</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9537</v>
+        <v>0.5642</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7698</v>
+        <v>-1.7221</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2688</v>
+        <v>1.8532</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2011</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0676</v>
+        <v>0.9314</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9826</v>
@@ -844,13 +844,13 @@
         <v>2.7164</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1391</v>
+        <v>-0.2765</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2568</v>
+        <v>-0.0225</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1177</v>
+        <v>-0.254</v>
       </c>
       <c r="V5" t="n">
         <v>0.3958</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9358</v>
+        <v>1.0597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9237</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0274</v>
+        <v>0.1361</v>
       </c>
       <c r="G6" t="n">
         <v>1.1802</v>
@@ -922,13 +922,13 @@
         <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8847</v>
+        <v>-0.7607</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1806</v>
+        <v>-0.2201</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.5406</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3299</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0987</v>
+        <v>-0.5898</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0119</v>
+        <v>2.7116</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1106</v>
+        <v>-3.3014</v>
       </c>
       <c r="G7" t="n">
         <v>0.9216</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9035</v>
+        <v>0.4125</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3645</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.539</v>
+        <v>0.3483</v>
       </c>
       <c r="V7" t="n">
         <v>-2.1179</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4355</v>
+        <v>-0.7542</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6973</v>
+        <v>-1.0977</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2618</v>
+        <v>0.3435</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1267</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.2395</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3645</v>
+        <v>-0.0359</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2853</v>
+        <v>-0.2036</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5178</v>
+        <v>-1.6462</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7642</v>
+        <v>0.6631</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.282</v>
+        <v>-2.3093</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6483</v>
@@ -1156,13 +1156,13 @@
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4141</v>
+        <v>0.2857</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2752</v>
+        <v>0.1741</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1389</v>
+        <v>0.1116</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8358</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1506</v>
+        <v>-1.9504</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0089</v>
+        <v>-0.8087</v>
       </c>
       <c r="F10" t="n">
         <v>-1.1418</v>
@@ -1234,10 +1234,10 @@
         <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3881</v>
+        <v>-0.1879</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1817</v>
+        <v>0.0185</v>
       </c>
       <c r="U10" t="n">
         <v>-0.2064</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8827</v>
+        <v>-2.6491</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3281</v>
+        <v>-1.1476</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4454</v>
+        <v>-1.5015</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3648</v>
+        <v>-2.0135</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6397</v>
+        <v>0.4523</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7252</v>
+        <v>-2.4658</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4892</v>
+        <v>-0.9116</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2358</v>
+        <v>1.0092</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2535</v>
+        <v>-1.9208</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8756</v>
+        <v>-1.1019</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4039</v>
+        <v>-0.5569</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5283</v>
+        <v>-0.545</v>
       </c>
       <c r="P11" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.2239</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-2.1344</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.1344</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.2001</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.0134</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1867</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.2821</v>
-      </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9583</v>
+        <v>-2.8038</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3478</v>
+        <v>-4.1674</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6105</v>
+        <v>1.3636</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0135</v>
+        <v>-3.3648</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4523</v>
+        <v>-2.6397</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4658</v>
+        <v>-0.7252</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9116</v>
+        <v>-2.4892</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0092</v>
+        <v>-1.2358</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9208</v>
+        <v>-1.2535</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1019</v>
+        <v>-0.8756</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5569</v>
+        <v>-1.4039</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.545</v>
+        <v>0.5283</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.109</v>
+        <v>0.279</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2423</v>
+        <v>0.1741</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1332</v>
+        <v>0.1049</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="W12" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="X12" t="n">
         <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-1.2239</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3299</v>
+        <v>-4.7143</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5425</v>
+        <v>-2.9815</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7874</v>
+        <v>-1.7329</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8657</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9944</v>
+        <v>-0.3788</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1508</v>
+        <v>-0.5897</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1564</v>
+        <v>0.2109</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6639</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.790900000000001</v>
+        <v>2.396199999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>8.275100000000002</v>
+        <v>8.880899999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.484299999999999</v>
+        <v>-6.484599999999999</v>
       </c>
       <c r="G14" t="n">
         <v>5.206900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5414</v>
+        <v>6.541399999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-1.3346</v>
@@ -1546,13 +1546,13 @@
         <v>19.4033</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2431</v>
+        <v>-1.6376</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4416</v>
+        <v>-0.8358</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8015999999999998</v>
+        <v>-0.8018</v>
       </c>
       <c r="V14" t="n">
         <v>-6.023899999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1537</v>
+        <v>4.5992</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0481</v>
+        <v>3.8479</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1056</v>
+        <v>0.7513</v>
       </c>
       <c r="G15" t="n">
         <v>2.885</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.3724</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1828</v>
+        <v>-0.0174</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7441</v>
+        <v>0.3898</v>
       </c>
       <c r="V15" t="n">
         <v>2.1179</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.019</v>
+        <v>3.8165</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5061</v>
+        <v>4.0066</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4871</v>
+        <v>-0.1901</v>
       </c>
       <c r="G16" t="n">
         <v>1.0595</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9823</v>
+        <v>-0.1848</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9567</v>
+        <v>-0.4562</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0255</v>
+        <v>0.2714</v>
       </c>
       <c r="V16" t="n">
         <v>2.1657</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8344</v>
+        <v>2.4406</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8228</v>
+        <v>4.023</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9884</v>
+        <v>-1.5824</v>
       </c>
       <c r="G17" t="n">
         <v>-0.07290000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5092</v>
+        <v>0.097</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1559</v>
+        <v>0.0443</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3533</v>
+        <v>0.0527</v>
       </c>
       <c r="V17" t="n">
         <v>0.2821</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7123</v>
+        <v>1.8669</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0683</v>
+        <v>1.1684</v>
       </c>
       <c r="F18" t="n">
-        <v>0.644</v>
+        <v>0.6985</v>
       </c>
       <c r="G18" t="n">
         <v>1.2155</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5211</v>
+        <v>-0.3665</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5933</v>
+        <v>-0.4932</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0722</v>
+        <v>0.1267</v>
       </c>
       <c r="V18" t="n">
         <v>0.0478</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3015</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1748</v>
+        <v>1.2749</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4763</v>
+        <v>-1.3401</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7322</v>
@@ -1936,13 +1936,13 @@
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3454</v>
+        <v>-0.1091</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0965</v>
+        <v>0.0036</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.249</v>
+        <v>-0.1127</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5894</v>
+        <v>-0.6251</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4956</v>
+        <v>-1.0952</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9062</v>
+        <v>0.4701</v>
       </c>
       <c r="G20" t="n">
         <v>0.9806</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7748</v>
+        <v>0.7391</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2053</v>
+        <v>0.1951</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9801</v>
+        <v>0.544</v>
       </c>
       <c r="V20" t="n">
         <v>2.1179</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0387</v>
+        <v>-1.4208</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1265</v>
+        <v>-0.1738</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1652</v>
+        <v>-1.247</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6585</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2914</v>
+        <v>0.9093</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6684</v>
+        <v>0.3681</v>
       </c>
       <c r="U21" t="n">
-        <v>0.623</v>
+        <v>0.5412</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4051</v>
+        <v>-2.6236</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6063</v>
+        <v>-0.9066</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7988</v>
+        <v>-1.717</v>
       </c>
       <c r="G22" t="n">
         <v>-1.215</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5278</v>
+        <v>0.3093</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6068</v>
+        <v>0.3065</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.079</v>
+        <v>0.0028</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7371</v>
+        <v>-2.9401</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8677</v>
+        <v>-1.0679</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8694</v>
+        <v>-1.8722</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5805</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2972</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2198</v>
+        <v>0.0196</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0774</v>
+        <v>0.0746</v>
       </c>
       <c r="V23" t="n">
         <v>0.5164</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0251</v>
+        <v>-3.0433</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5875</v>
+        <v>-2.605</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4376</v>
+        <v>-0.4383</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4854</v>
+        <v>-1.603</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6986</v>
+        <v>-1.8867</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7868</v>
+        <v>0.2836</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5633</v>
+        <v>1.0645</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3347</v>
+        <v>0.4861</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.898</v>
+        <v>0.5784</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9221</v>
+        <v>-2.6675</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.0333</v>
+        <v>-2.3728</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1112</v>
+        <v>-0.2948</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q24" t="n">
         <v>-3.8806</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7887</v>
+        <v>0.3642</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0206</v>
+        <v>0.2111</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2319</v>
+        <v>0.1531</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6119</v>
+        <v>0.3299</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2239</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4131</v>
+        <v>-3.1285</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7051</v>
+        <v>-1.9879</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.708</v>
+        <v>-1.1406</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.603</v>
+        <v>-2.4854</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8867</v>
+        <v>-0.6986</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2836</v>
+        <v>-1.7868</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0645</v>
+        <v>-0.5633</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4861</v>
+        <v>1.3347</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5784</v>
+        <v>-1.898</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6675</v>
+        <v>-1.9221</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.3728</v>
+        <v>-2.0333</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2948</v>
+        <v>0.1112</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q25" t="n">
         <v>-3.8806</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0056</v>
+        <v>0.6853</v>
       </c>
       <c r="T25" t="n">
-        <v>0.111</v>
+        <v>0.6202</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1166</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3299</v>
+        <v>0.6119</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="26">
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.790600000000001</v>
+        <v>-1.123300000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>6.484400000000001</v>
+        <v>6.484399999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.274999999999999</v>
+        <v>-7.607800000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.2069</v>
+        <v>-5.206899999999999</v>
       </c>
       <c r="H26" t="n">
         <v>-6.541600000000001</v>
@@ -2458,7 +2458,7 @@
         <v>12.1443</v>
       </c>
       <c r="K26" t="n">
-        <v>8.5848</v>
+        <v>8.584799999999998</v>
       </c>
       <c r="L26" t="n">
         <v>3.559500000000001</v>
@@ -2482,13 +2482,13 @@
         <v>14.5525</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2432</v>
+        <v>2.9104</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8016999999999996</v>
+        <v>0.8016999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4415</v>
+        <v>2.1087</v>
       </c>
       <c r="V26" t="n">
         <v>6.0239</v>
